--- a/Paris_visited_out.xlsx
+++ b/Paris_visited_out.xlsx
@@ -369,7 +369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
@@ -487,7 +487,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Metro: Place de Clichy</t>
+          <t>&lt;a href='https://www.lalahotel.com/' target='_blank'&gt;LALA Hôtel&lt;/a&gt;</t>
         </is>
       </c>
       <c r="B4" t="e">
@@ -495,504 +495,538 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>subway</t>
+          <t>hotel</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>48.88373820753087, 2.3281385450929686</t>
+          <t>48.88343165064482, 2.325123514202397</t>
         </is>
       </c>
       <c r="E4" t="b">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>2.32813854509297</v>
+        <v>2.3251235142024</v>
       </c>
       <c r="G4">
-        <v>48.8837382075309</v>
+        <v>48.8834316506448</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Metro: Place de Clichy |</t>
+          <t>&lt;a href='https://www.lalahotel.com/' target='_blank'&gt;LALA Hôtel&lt;/a&gt; |</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Le Grand Epicerie de Paris</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Multi-story gourmet food hall and market; lots of food counters to sit and eat, everything from crepes to whelks. We should def plan to get lunch (or dinner) here one day; also great shopping, e.g. food souvenirs (sel de mer, mustard, jams, etc).</t>
-        </is>
+          <t>Metro: Place de Clichy</t>
+        </is>
+      </c>
+      <c r="B5" t="e">
+        <v>#N/A</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>market</t>
+          <t>subway</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>48.85969027625157, 2.281738258736061</t>
+          <t>48.88373820753087, 2.3281385450929686</t>
         </is>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>2.28173825873606</v>
+        <v>2.32813854509297</v>
       </c>
       <c r="G5">
-        <v>48.8596902762516</v>
+        <v>48.8837382075309</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Le Grand Epicerie de Paris | Multi-story gourmet food hall and market; lots of food counters to sit and eat, everything from crepes to whelks. We should def plan to get lunch (or dinner) here one day; also great shopping, e.g. food souvenirs (sel de mer, mustard, jams, etc).</t>
+          <t>Metro: Place de Clichy |</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Le Grand Epicerie de Paris</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Multi-story gourmet food hall and market; lots of food counters to sit and eat, everything from crepes to whelks. We should def plan to get lunch (or dinner) here one day; also great shopping, e.g. food souvenirs (sel de mer, mustard, jams, etc).</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>48.85969027625157, 2.281738258736061</t>
+        </is>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>2.28173825873606</v>
+      </c>
+      <c r="G6">
+        <v>48.8596902762516</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Le Grand Epicerie de Paris | Multi-story gourmet food hall and market; lots of food counters to sit and eat, everything from crepes to whelks. We should def plan to get lunch (or dinner) here one day; also great shopping, e.g. food souvenirs (sel de mer, mustard, jams, etc).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Place de la Concorde</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Photogenic, tourist-y, we'll likely be in the area at some point. (And in case we want to replicate the cover of "A Paris".)
 Dev &amp; Joel visted, May 25, 2026.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>landmark/photo opp</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>48.86573896567691, 2.3220135406280296</t>
         </is>
       </c>
-      <c r="E6" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6">
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7">
         <v>2.32201354062803</v>
       </c>
-      <c r="G6">
+      <c r="G7">
         <v>48.8657389656769</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Place de la Concorde | Photogenic, tourist-y, we'll likely be in the area at some point. (And in case we want to replicate the cover of "A Paris".)
 Dev &amp; Joel visted, May 25, 2026.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>&lt;a href='https://www.lamachinedumoulinrouge.com/le-bar-a-bulles/' target='_blank'&gt;Le Bar à Bulles&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Rooftop bar behind the windmill blades at Moulen Rouge
 Visted May 25, 2026, sat behind the blades of the windmill. Big fun.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>bar</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>48.88471002715455, 2.332271841758535</t>
         </is>
       </c>
-      <c r="E7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7">
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8">
         <v>2.33227184175853</v>
       </c>
-      <c r="G7">
+      <c r="G8">
         <v>48.8847100271545</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>&lt;a href='https://www.lamachinedumoulinrouge.com/le-bar-a-bulles/' target='_blank'&gt;Le Bar à Bulles&lt;/a&gt; | Rooftop bar behind the windmill blades at Moulen Rouge
 Visted May 25, 2026, sat behind the blades of the windmill. Big fun.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Marché couvert des Enfants Rouges</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Classic outdoor marketplace with vendors selling produce, meat &amp; seafood, plus wine, cheese &amp; more.</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>48.86462477434395, 2.3620981386226587</t>
-        </is>
-      </c>
-      <c r="E8" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>2.36209813862266</v>
-      </c>
-      <c r="G8">
-        <v>48.864624774344</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Marché couvert des Enfants Rouges | Classic outdoor marketplace with vendors selling produce, meat &amp; seafood, plus wine, cheese &amp; more.</t>
-        </is>
-      </c>
-    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Les Domaines Qui Montent Paris Cardinet</t>
+          <t>Marché couvert des Enfants Rouges</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Great selection. Knowledgable helpful staff. Cured meats and cheeses—small but very fine selection. Visited May 18, 2026.</t>
+          <t>Classic outdoor marketplace with vendors selling produce, meat &amp; seafood, plus wine, cheese &amp; more.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wine store</t>
+          <t>market</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>48.882116, 2.328847</t>
+          <t>48.86462477434395, 2.3620981386226587</t>
         </is>
       </c>
       <c r="E9" t="b">
         <v>1</v>
       </c>
       <c r="F9">
-        <v>2.328847</v>
+        <v>2.36209813862266</v>
       </c>
       <c r="G9">
-        <v>48.882116</v>
+        <v>48.864624774344</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Les Domaines Qui Montent Paris Cardinet | Great selection. Knowledgable helpful staff. Cured meats and cheeses—small but very fine selection. Visited May 18, 2026.</t>
+          <t>Marché couvert des Enfants Rouges | Classic outdoor marketplace with vendors selling produce, meat &amp; seafood, plus wine, cheese &amp; more.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cafe l'Entracte</t>
+          <t>Les Domaines Qui Montent Paris Cardinet</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>So small, small selection, neighborhood, great dark hole in the wall. Visited May 18, 2026.</t>
+          <t>Great selection. Knowledgable helpful staff. Cured meats and cheeses—small but very fine selection. Visited May 18, 2026.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Wine store</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>48.884068, 2.326317</t>
+          <t>48.882116, 2.328847</t>
         </is>
       </c>
       <c r="E10" t="b">
         <v>1</v>
       </c>
       <c r="F10">
-        <v>2.326317</v>
+        <v>2.328847</v>
       </c>
       <c r="G10">
-        <v>48.884068</v>
+        <v>48.882116</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Cafe l'Entracte | So small, small selection, neighborhood, great dark hole in the wall. Visited May 18, 2026.</t>
+          <t>Les Domaines Qui Montent Paris Cardinet | Great selection. Knowledgable helpful staff. Cured meats and cheeses—small but very fine selection. Visited May 18, 2026.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Cafe l'Entracte</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>So small, small selection, neighborhood, great dark hole in the wall. Visited May 18, 2026.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bar</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>48.884068, 2.326317</t>
+        </is>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>2.326317</v>
+      </c>
+      <c r="G11">
+        <v>48.884068</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Cafe l'Entracte | So small, small selection, neighborhood, great dark hole in the wall. Visited May 18, 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>&lt;a href='https://www.rooster-restaurant.com/reservation/' target='_blank'&gt;ROOSTER PAR FRÉDÉRIC DUCA&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t xml:space="preserve">After training in prestigious houses (from Passedat to Darroze), Frédéric Duca has set up shop in the more working-class part of the 17th arrondissement. In a former street corner cafe, the Marseille-born chef signs dishes which pay numerous tributes to his Mediterranean and Provençal roots. The lunchtime menu is at delicious eater-friendly prices. More ambitious in the evenings.
 Vistined Thursday, May 21, 2026. </t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>restaurant</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>48.88687437146972, 2.3131238164807524</t>
         </is>
       </c>
-      <c r="E11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F11">
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12">
         <v>2.31312381648075</v>
       </c>
-      <c r="G11">
+      <c r="G12">
         <v>48.8868743714697</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>&lt;a href='https://www.rooster-restaurant.com/reservation/' target='_blank'&gt;ROOSTER PAR FRÉDÉRIC DUCA&lt;/a&gt; | After training in prestigious houses (from Passedat to Darroze), Frédéric Duca has set up shop in the more working-class part of the 17th arrondissement. In a former street corner cafe, the Marseille-born chef signs dishes which pay numerous tributes to his Mediterranean and Provençal roots. The lunchtime menu is at delicious eater-friendly prices. More ambitious in the evenings.
 Vistined Thursday, May 21, 2026.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Le Wagon Bleu</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Corsican cuisine in a wood-paneled railway carriage which becomes a late-night club on the weekend.
 Great meal with excellent dose of Clementine liquor at meal's end.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>restaurant</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>48.883029954751635, 2.320535551879477</t>
         </is>
       </c>
-      <c r="E12" t="b">
-        <v>1</v>
-      </c>
-      <c r="F12">
+      <c r="E13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13">
         <v>2.32053555187948</v>
       </c>
-      <c r="G12">
+      <c r="G13">
         <v>48.8830299547516</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Le Wagon Bleu | Corsican cuisine in a wood-paneled railway carriage which becomes a late-night club on the weekend.
 Great meal with excellent dose of Clementine liquor at meal's end.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>La Samaritaine</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FANCY department store. </t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>store</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>48.859038971904695, 2.342141408689555</t>
-        </is>
-      </c>
-      <c r="E13" t="b">
-        <v>1</v>
-      </c>
-      <c r="F13">
-        <v>2.34214140868955</v>
-      </c>
-      <c r="G13">
-        <v>48.8590389719047</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>La Samaritaine | FANCY department store.</t>
-        </is>
-      </c>
-    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>La Samaritaine</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FANCY department store. </t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>48.859038971904695, 2.342141408689555</t>
+        </is>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>2.34214140868955</v>
+      </c>
+      <c r="G14">
+        <v>48.8590389719047</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>La Samaritaine | FANCY department store.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Big Love</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>BigLove is a Neapolitan trattoria created by the cheerful Big Mamma team. Through the big glass door on rue Debeylleme, customers are warmly welcomed into an authentic, intimate setting with the feel of a large Italian grocery shop and cosy cafés. BigLove also offers gourmet brunches and traditional Neapolitan dishes, all 100% vegaterian!
 Visted May 19, 2026</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>restaurant</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>48.86246746812821, 2.3636752266517496</t>
         </is>
       </c>
-      <c r="E14" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14">
+      <c r="E15" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15">
         <v>2.36367522665175</v>
       </c>
-      <c r="G14">
+      <c r="G15">
         <v>48.8624674681282</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Big Love | BigLove is a Neapolitan trattoria created by the cheerful Big Mamma team. Through the big glass door on rue Debeylleme, customers are warmly welcomed into an authentic, intimate setting with the feel of a large Italian grocery shop and cosy cafés. BigLove also offers gourmet brunches and traditional Neapolitan dishes, all 100% vegaterian!
 Visted May 19, 2026</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Habib Beirut</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Lebanese restaurant
 Visited May 17, 2026. Excellent wine, inexpensive, great flavors.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>restaurant</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>48.880146211484224, 2.321841803042917</t>
         </is>
       </c>
-      <c r="E15" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15">
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16">
         <v>2.32184180304292</v>
       </c>
-      <c r="G15">
+      <c r="G16">
         <v>48.8801462114842</v>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Habib Beirut | Lebanese restaurant
 Visited May 17, 2026. Excellent wine, inexpensive, great flavors.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>&lt;a href='https://pharmacie-citypharma.fr/en/' target='_blank'&gt;Citypharma&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Crazy-busy discount drugstore, with floors of toilettries.</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>store</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>48.85290456181854, 2.3333528975762388</t>
-        </is>
-      </c>
-      <c r="E16" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16">
-        <v>2.33335289757624</v>
-      </c>
-      <c r="G16">
-        <v>48.8529045618185</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>&lt;a href='https://pharmacie-citypharma.fr/en/' target='_blank'&gt;Citypharma&lt;/a&gt; | Crazy-busy discount drugstore, with floors of toilettries.</t>
-        </is>
-      </c>
-    </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>&lt;a href='https://pharmacie-citypharma.fr/en/' target='_blank'&gt;Citypharma&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Crazy-busy discount drugstore, with floors of toilettries.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>48.85290456181854, 2.3333528975762388</t>
+        </is>
+      </c>
+      <c r="E17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>2.33335289757624</v>
+      </c>
+      <c r="G17">
+        <v>48.8529045618185</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>&lt;a href='https://pharmacie-citypharma.fr/en/' target='_blank'&gt;Citypharma&lt;/a&gt; | Crazy-busy discount drugstore, with floors of toilettries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>VETRA - Vêtement de travail depuis 1927 - Paris</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Fancy French "workwear" https://www.vetra.fr/fr/vestes-de-travail-homme/2556-veste-workwear-moleskine-authentique-made-in-france.html</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>store</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>48.8616663, 2.3647518</t>
         </is>
       </c>
-      <c r="E17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17">
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18">
         <v>2.3647518</v>
       </c>
-      <c r="G17">
+      <c r="G18">
         <v>48.8616663</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>VETRA - Vêtement de travail depuis 1927 - Paris | Fancy French "workwear" https://www.vetra.fr/fr/vestes-de-travail-homme/2556-veste-workwear-moleskine-authentique-made-in-france.html</t>
         </is>
